--- a/countries/br/2000-2004.xlsx
+++ b/countries/br/2000-2004.xlsx
@@ -769,11 +769,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>8.164084760255491</v>
+        <v>8.366943136412269</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -917,11 +917,11 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7177406817455556</v>
+        <v>0.7355748558723815</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1065,11 +1065,11 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1815901164384272</v>
+        <v>0.1861022053288011</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1213,11 +1213,11 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.060808085270053</v>
+        <v>1.08716668049673</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1361,11 +1361,11 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1063106694338893</v>
+        <v>0.1089522404614816</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1509,11 +1509,11 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>14.21689709078066</v>
+        <v>14.57015367036246</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1657,11 +1657,11 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5861453125544168</v>
+        <v>0.6007096501119529</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1805,11 +1805,11 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1850380300416885</v>
+        <v>0.1896357915059302</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.978632811058992</v>
+        <v>1.002949543275153</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2101,11 +2101,11 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1068853217010995</v>
+        <v>0.1095411714910032</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>18.48254087028207</v>
+        <v>18.94178870250073</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2397,11 +2397,11 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.507992604213828</v>
+        <v>0.5206150300970258</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2545,11 +2545,11 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2074494684628868</v>
+        <v>0.2126041016572696</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2693,11 +2693,11 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8987561459167727</v>
+        <v>0.921088130171661</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2841,11 +2841,11 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.08274992647827062</v>
+        <v>0.08480606825109922</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2989,11 +2989,11 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>16.60630121784072</v>
+        <v>17.01892889111295</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3137,11 +3137,11 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.470065554577954</v>
+        <v>0.4817455821486054</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3285,11 +3285,11 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2298609068840851</v>
+        <v>0.235572411808609</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3433,11 +3433,11 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.753943774579799</v>
+        <v>0.7726775107322373</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3581,11 +3581,11 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.07125688113406636</v>
+        <v>0.07302744766066878</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3729,11 +3729,11 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>14.17609677980874</v>
+        <v>14.52833956726644</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3877,11 +3877,11 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4832825567237888</v>
+        <v>0.4952909958276003</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4025,11 +4025,11 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2218157751431421</v>
+        <v>0.2273273773953076</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4173,11 +4173,11 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8516346600055351</v>
+        <v>0.8727957857508962</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4321,11 +4321,11 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1155051057092527</v>
+        <v>0.118375136933826</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4469,11 +4469,11 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6.857325504619467</v>
+        <v>7.027713975280326</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4617,11 +4617,11 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.4103017187880918</v>
+        <v>0.420496755078367</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4765,11 +4765,11 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1959564231186825</v>
+        <v>0.2008254810668391</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4913,11 +4913,11 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7119941590734534</v>
+        <v>0.7296855455771663</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5061,11 +5061,11 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1356179350616102</v>
+        <v>0.1389877229670793</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5209,11 +5209,11 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.517916124806692</v>
+        <v>4.630175754098209</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5357,11 +5357,11 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4850065135254195</v>
+        <v>0.4970577889161649</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5505,11 +5505,11 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2344581250217667</v>
+        <v>0.2402838600447811</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5653,11 +5653,11 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8131329581024509</v>
+        <v>0.8333374067729542</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5801,11 +5801,11 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1402151531992919</v>
+        <v>0.1436991712032515</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5949,11 +5949,11 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.4605559531399</v>
+        <v>3.546542659778608</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6097,11 +6097,11 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.9884018996015658</v>
+        <v>1.012961370777018</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6245,11 +6245,11 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2591681725118059</v>
+        <v>0.2656078943142066</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6393,11 +6393,11 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.9136971048642382</v>
+        <v>0.9364003369392205</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6541,11 +6541,11 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1752689414991148</v>
+        <v>0.1796239640040643</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6689,11 +6689,11 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0005746522672102127</v>
+        <v>0.0005889310295215224</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6837,11 +6837,11 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.040590200863465</v>
+        <v>2.091294085830926</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6985,11 +6985,11 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4568485524321191</v>
+        <v>0.4682001684696103</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7133,11 +7133,11 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1718210278958536</v>
+        <v>0.1760903778269352</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7281,11 +7281,11 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.057934823934001</v>
+        <v>1.084222025349123</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7429,11 +7429,11 @@
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1350432827943999</v>
+        <v>0.1383987919375578</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7577,11 +7577,11 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.509506450906998</v>
+        <v>2.571861805920488</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7725,11 +7725,11 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4160482414601939</v>
+        <v>0.4263860653735822</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7873,11 +7873,11 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2522723453052834</v>
+        <v>0.2585407219599483</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8021,11 +8021,11 @@
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.114825398387812</v>
+        <v>1.142526197271754</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8169,11 +8169,11 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.1402151531992919</v>
+        <v>0.1436991712032515</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8317,11 +8317,11 @@
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.002298609068840851</v>
+        <v>0.00235572411808609</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8465,11 +8465,11 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.028887045410801</v>
+        <v>4.128995447975393</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8613,11 +8613,11 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.3867409758324731</v>
+        <v>0.3963505828679845</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8761,11 +8761,11 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.18906059591216</v>
+        <v>0.1937583087125808</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8909,11 +8909,11 @@
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.095861873569876</v>
+        <v>1.123091473297543</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9057,11 +9057,11 @@
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.154006807612337</v>
+        <v>0.157833515911768</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9205,11 +9205,11 @@
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.004597218137681701</v>
+        <v>0.004711448236172179</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9353,11 +9353,11 @@
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.2708156499063</v>
+        <v>4.376935411403954</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9501,11 +9501,11 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4689162500435335</v>
+        <v>0.4805677200895623</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9649,11 +9649,11 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.1465363281386042</v>
+        <v>0.1501774125279882</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9797,11 +9797,11 @@
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.7895722151468322</v>
+        <v>0.8091912345625718</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9945,11 +9945,11 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1235502374501957</v>
+        <v>0.1266201713471273</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10093,11 +10093,11 @@
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.002298609068840851</v>
+        <v>0.00235572411808609</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10241,11 +10241,11 @@
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>17.85523834457329</v>
+        <v>18.26078206685044</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10389,11 +10389,11 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.645465765766783</v>
+        <v>3.72826475884392</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10537,11 +10537,11 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.100382718318717</v>
+        <v>2.148088439707334</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10685,11 +10685,11 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.2172418528533807</v>
+        <v>0.222176038997545</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10833,11 +10833,11 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.767429800237948</v>
+        <v>1.807573205003525</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10981,11 +10981,11 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1412355649099002</v>
+        <v>0.1444434300532342</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11129,11 +11129,11 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.001701633312167473</v>
+        <v>0.001740282289798002</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11277,11 +11277,11 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>28.64869844365157</v>
+        <v>29.29939263103917</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11425,11 +11425,11 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.294362092356228</v>
+        <v>3.369186513048932</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11573,11 +11573,11 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.269978838431409</v>
+        <v>2.321536574590535</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11721,11 +11721,11 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.177537075569473</v>
+        <v>0.1815694522355916</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11869,11 +11869,11 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.153707385649547</v>
+        <v>1.179911392483046</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12017,11 +12017,11 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.106635687562495</v>
+        <v>0.1090576901606748</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12165,11 +12165,11 @@
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001701633312167473</v>
+        <v>0.001740282289798002</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12313,11 +12313,11 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>42.74899927937531</v>
+        <v>43.71995177840201</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12461,11 +12461,11 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.344269845963558</v>
+        <v>4.442940685854301</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12609,11 +12609,11 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.681206888871881</v>
+        <v>2.742104794625052</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12757,11 +12757,11 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.2206451194777156</v>
+        <v>0.225656603577141</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12905,11 +12905,11 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.636971246305109</v>
+        <v>1.674151562785678</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13053,11 +13053,11 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.1610879535518541</v>
+        <v>0.1647467234342109</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13201,11 +13201,11 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001134422208111649</v>
+        <v>0.001160188193198668</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13349,11 +13349,11 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>53.00871372953706</v>
+        <v>54.21269379769077</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13497,11 +13497,11 @@
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.082785526993823</v>
+        <v>4.175517307322007</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13645,11 +13645,11 @@
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.377181737097959</v>
+        <v>2.431174358847809</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13793,11 +13793,11 @@
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.2036287863560409</v>
+        <v>0.2082537806791609</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13941,11 +13941,11 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.368680394086704</v>
+        <v>1.399767055094193</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14089,11 +14089,11 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.1179799096436114</v>
+        <v>0.1206595720926615</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14237,11 +14237,11 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.001134422208111649</v>
+        <v>0.001160188193198668</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14385,11 +14385,11 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>55.52316055381653</v>
+        <v>56.78425092791562</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14533,11 +14533,11 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>4.213244080926663</v>
+        <v>4.308938949539854</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -14681,11 +14681,11 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.667593822374542</v>
+        <v>2.728182536306668</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -14829,11 +14829,11 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.2416319303277811</v>
+        <v>0.2471200851513163</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -14977,11 +14977,11 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.398175371497607</v>
+        <v>1.429931948117358</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15125,11 +15125,11 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.1599535313437425</v>
+        <v>0.1635865352410122</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15273,11 +15273,11 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.001134422208111649</v>
+        <v>0.001160188193198668</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -15421,11 +15421,11 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>26.08490425331925</v>
+        <v>26.67736731441018</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -15569,11 +15569,11 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.810524197047027</v>
+        <v>3.897072140954326</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -15717,11 +15717,11 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.22233310569072</v>
+        <v>2.272808670476191</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -15865,11 +15865,11 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0.1781042866735288</v>
+        <v>0.1821495463321909</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16013,11 +16013,11 @@
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1.1247796193427</v>
+        <v>1.150326593556479</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -16161,11 +16161,11 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1060684764584391</v>
+        <v>0.1084775960640755</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -16309,11 +16309,11 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.001701633312167473</v>
+        <v>0.001740282289798002</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -16457,11 +16457,11 @@
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>13.96587180406251</v>
+        <v>14.28307684646881</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -16605,11 +16605,11 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.948923706436648</v>
+        <v>4.038615100524564</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -16753,11 +16753,11 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.354493292935727</v>
+        <v>2.407970594983836</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -16901,11 +16901,11 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0.1820747644019196</v>
+        <v>0.1862102050083863</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -17049,11 +17049,11 @@
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1.339185416675801</v>
+        <v>1.369602162071028</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -17197,11 +17197,11 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0.1383995093896211</v>
+        <v>0.1415429595702375</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -17345,11 +17345,11 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0005672111040558243</v>
+        <v>0.0005800940965993341</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17493,11 +17493,11 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>9.084453042558081</v>
+        <v>9.290787051134934</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -17641,11 +17641,11 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>4.512731543868138</v>
+        <v>4.615228632544301</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -17789,11 +17789,11 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.75210827687886</v>
+        <v>2.814616556699969</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -17937,11 +17937,11 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.2200779083736598</v>
+        <v>0.2250765094805416</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -18085,11 +18085,11 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1.547351891864289</v>
+        <v>1.582496695522984</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18233,11 +18233,11 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.1815075532978638</v>
+        <v>0.1856301109117869</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18381,11 +18381,11 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0.002836055520279122</v>
+        <v>0.00290047048299667</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -18529,11 +18529,11 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>5.953447748169932</v>
+        <v>6.08866763790661</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -18677,11 +18677,11 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.707858987212923</v>
+        <v>3.792075109469847</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -18825,11 +18825,11 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.352791659623559</v>
+        <v>2.406230312694038</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -18973,11 +18973,11 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0.1809403421938079</v>
+        <v>0.1850500168151876</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -19121,11 +19121,11 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1.492899625874929</v>
+        <v>1.526807662249447</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -19269,11 +19269,11 @@
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.145206042638291</v>
+        <v>0.1485040887294295</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -19417,11 +19417,11 @@
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.002268844416223297</v>
+        <v>0.002320376386397336</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -19565,11 +19565,11 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>6.999385024048871</v>
+        <v>7.158361152035782</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -19713,11 +19713,11 @@
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>4.352210801420339</v>
+        <v>4.45106200320669</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -19861,11 +19861,11 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2.681206888871881</v>
+        <v>2.742104794625052</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -20009,11 +20009,11 @@
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.2024943641479293</v>
+        <v>0.2070935924859623</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20157,11 +20157,11 @@
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2.141789128914793</v>
+        <v>2.190435308759085</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -20305,11 +20305,11 @@
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.1281897095166163</v>
+        <v>0.1311012658314495</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -20453,11 +20453,11 @@
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.002836055520279122</v>
+        <v>0.00290047048299667</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -20601,11 +20601,11 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>7.803123158495975</v>
+        <v>7.980354486917039</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -20749,11 +20749,11 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.865543674140442</v>
+        <v>3.953341268324462</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -20897,11 +20897,11 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2.393630859115579</v>
+        <v>2.44799708764919</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -21045,11 +21045,11 @@
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0.1934189864830361</v>
+        <v>0.1978120869403729</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -21193,11 +21193,11 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1.928517753789802</v>
+        <v>1.972319928437736</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -21341,11 +21341,11 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.1015307876259925</v>
+        <v>0.1038368432912808</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -21489,11 +21489,11 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0.006239322144614068</v>
+        <v>0.006381035062592675</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -21637,11 +21637,11 @@
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>9.457677949026815</v>
+        <v>9.672488966697296</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -21785,11 +21785,11 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>3.669855843241183</v>
+        <v>3.753208804997691</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -21933,11 +21933,11 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>1.888812976505895</v>
+        <v>1.931713341675783</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -22081,11 +22081,11 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1707305423208031</v>
+        <v>0.1746083230763996</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -22229,11 +22229,11 @@
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>1.494601259187097</v>
+        <v>1.528547944539246</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -22377,11 +22377,11 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.07260302131914551</v>
+        <v>0.07425204436471476</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -22525,11 +22525,11 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>0.004537688832446594</v>
+        <v>0.004640752772794673</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -22673,11 +22673,11 @@
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>53.94292487294793</v>
+        <v>55.13850306379735</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -22821,11 +22821,11 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.539426724969208</v>
+        <v>3.617873739298698</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -22969,11 +22969,11 @@
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.8756131641543007</v>
+        <v>0.8950200466166295</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -23117,11 +23117,11 @@
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>2.065505909300644</v>
+        <v>2.11128529230679</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -23265,11 +23265,11 @@
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>0.1904724733285107</v>
+        <v>0.1946940600445643</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -23413,11 +23413,11 @@
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>1.925452620088504</v>
+        <v>1.968127895215199</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -23561,11 +23561,11 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0.165823094427174</v>
+        <v>0.1694983581564442</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -23709,11 +23709,11 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>0.003361278941091366</v>
+        <v>0.003435777530198194</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -23857,11 +23857,11 @@
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>124.7437840617827</v>
+        <v>127.5085757007154</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -24005,11 +24005,11 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>3.63186189584922</v>
+        <v>3.712357621379149</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -24153,11 +24153,11 @@
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0.8862572141344233</v>
+        <v>0.9059000087955905</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -24301,11 +24301,11 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>2.140574472318351</v>
+        <v>2.188017657147883</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -24449,11 +24449,11 @@
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>0.1809488496620852</v>
+        <v>0.1849593570423361</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -24597,11 +24597,11 @@
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>1.479522947237049</v>
+        <v>1.512314742875572</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -24745,11 +24745,11 @@
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>0.09859751560534671</v>
+        <v>0.1007828075524804</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -24893,11 +24893,11 @@
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>0.003921492097939926</v>
+        <v>0.00400840711856456</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -25041,11 +25041,11 @@
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>154.8373144213737</v>
+        <v>158.2690919285798</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -25189,11 +25189,11 @@
         <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>4.204959955305298</v>
+        <v>4.29815769027794</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -25337,11 +25337,11 @@
         <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>0.8128692905872619</v>
+        <v>0.8308855327195965</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -25485,11 +25485,11 @@
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>2.489027055878156</v>
+        <v>2.544193261111763</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -25633,11 +25633,11 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>0.197755244367542</v>
+        <v>0.2021382446933271</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -25781,11 +25781,11 @@
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>1.479522947237049</v>
+        <v>1.512314742875572</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -25929,11 +25929,11 @@
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>0.1322103050162604</v>
+        <v>0.1351405828544623</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -26077,11 +26077,11 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>0.002801065784242805</v>
+        <v>0.002863147941831828</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -26225,11 +26225,11 @@
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>81.44490916895748</v>
+        <v>83.25003481587896</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -26373,11 +26373,11 @@
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>4.777497801604527</v>
+        <v>4.883385129588366</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -26521,11 +26521,11 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0.7478845643928288</v>
+        <v>0.7644605004690982</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -26669,11 +26669,11 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>2.838600065751658</v>
+        <v>2.901514124252375</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -26817,11 +26817,11 @@
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0.211760573288756</v>
+        <v>0.2164539844024862</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -26965,11 +26965,11 @@
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>1.533303410294511</v>
+        <v>1.567287183358743</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -27113,11 +27113,11 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0.1159641234676521</v>
+        <v>0.1185343247918377</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -27261,11 +27261,11 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0.003921492097939926</v>
+        <v>0.00400840711856456</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -27409,11 +27409,11 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>33.04193220408497</v>
+        <v>33.77426575143661</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -27557,11 +27557,11 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>4.2822693709504</v>
+        <v>4.377180573472499</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -27705,11 +27705,11 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>0.4526522307336373</v>
+        <v>0.4626847074000234</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -27853,11 +27853,11 @@
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>2.753447665910677</v>
+        <v>2.814474426820687</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -28001,11 +28001,11 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0.2112003601319074</v>
+        <v>0.2158813548141199</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -28149,11 +28149,11 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>1.211180845106589</v>
+        <v>1.238025170048083</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -28297,11 +28297,11 @@
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>0.1686241602114168</v>
+        <v>0.1723615060982761</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -28445,11 +28445,11 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>0.005041918411637048</v>
+        <v>0.005153666295297291</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -28593,11 +28593,11 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>12.90058857590866</v>
+        <v>13.18651416090067</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -28741,11 +28741,11 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>3.686202572063531</v>
+        <v>3.767902691450686</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -28889,11 +28889,11 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>0.4050341124015095</v>
+        <v>0.4140111923888823</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -29037,11 +29037,11 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>2.417879984958389</v>
+        <v>2.471469303389234</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -29185,11 +29185,11 @@
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.183749915446328</v>
+        <v>0.1878225049841679</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -29333,11 +29333,11 @@
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>1.034153487542443</v>
+        <v>1.057074220124311</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -29481,11 +29481,11 @@
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>0.1322103050162604</v>
+        <v>0.1351405828544623</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -29629,11 +29629,11 @@
         <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>0.001680639470545683</v>
+        <v>0.001717888765099097</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -29777,11 +29777,11 @@
         <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>8.214405518870448</v>
+        <v>8.396467654216019</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -29925,11 +29925,11 @@
         <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>4.297395126185311</v>
+        <v>4.39264157235839</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -30073,11 +30073,11 @@
         <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>0.4403275412829688</v>
+        <v>0.4500868564559634</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -30221,11 +30221,11 @@
         <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>2.807788342124987</v>
+        <v>2.870019496892224</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -30369,11 +30369,11 @@
         <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>0.1921531127990564</v>
+        <v>0.1964119488096634</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -30517,11 +30517,11 @@
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>1.343391150122849</v>
+        <v>1.373165752902545</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -30665,11 +30665,11 @@
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>0.142854354996383</v>
+        <v>0.1460205450334232</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -30813,11 +30813,11 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>0.003921492097939926</v>
+        <v>0.00400840711856456</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -30961,11 +30961,11 @@
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>6.709112766418365</v>
+        <v>6.857811950275595</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -31109,11 +31109,11 @@
         <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>4.503553567905581</v>
+        <v>4.603369260877214</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -31257,11 +31257,11 @@
         <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>0.4128770965973894</v>
+        <v>0.4220280066260115</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -31405,11 +31405,11 @@
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>2.915909481396759</v>
+        <v>2.980537007446933</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -31553,11 +31553,11 @@
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>0.197755244367542</v>
+        <v>0.2021382446933271</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -31701,11 +31701,11 @@
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>1.490727210374021</v>
+        <v>1.523767334642899</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -31849,11 +31849,11 @@
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>0.09131474456631541</v>
+        <v>0.0933386229037176</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -31997,11 +31997,11 @@
         <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>0.005041918411637048</v>
+        <v>0.005153666295297291</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -32145,11 +32145,11 @@
         <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>4.927634927639941</v>
+        <v>5.036849859270553</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -32293,11 +32293,11 @@
         <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>4.316442373518162</v>
+        <v>4.412110978362848</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -32441,11 +32441,11 @@
         <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>0.3871072913823556</v>
+        <v>0.3956870455611587</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -32589,11 +32589,11 @@
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>2.762971289577102</v>
+        <v>2.824209129822915</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -32737,11 +32737,11 @@
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>0.1999960969949362</v>
+        <v>0.2044287630467926</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -32885,11 +32885,11 @@
         <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>1.495769128785658</v>
+        <v>1.528921000938196</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -33033,11 +33033,11 @@
         <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0.1036394340169838</v>
+        <v>0.1059364738477777</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -33181,11 +33181,11 @@
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.001680639470545683</v>
+        <v>0.001717888765099097</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -33329,11 +33329,11 @@
         <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>5.179170635064946</v>
+        <v>5.29396054444705</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -33477,11 +33477,11 @@
         <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>4.59710916509929</v>
+        <v>4.698998402134396</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -33625,11 +33625,11 @@
         <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>0.409515817656298</v>
+        <v>0.4185922290958133</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -33773,11 +33773,11 @@
         <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>2.944480352396036</v>
+        <v>3.009741116453618</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -33921,11 +33921,11 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>0.2100799338182103</v>
+        <v>0.2147360956373871</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -34069,11 +34069,11 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>1.706969488917565</v>
+        <v>1.744802355752316</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -34217,11 +34217,11 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>0.09243517088001255</v>
+        <v>0.09448388208045033</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -34365,11 +34365,11 @@
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>0.002801065784242805</v>
+        <v>0.002863147941831828</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -34513,11 +34513,11 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>7.779680109155965</v>
+        <v>7.95210709364372</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -34661,11 +34661,11 @@
         <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>4.18871377375669</v>
+        <v>4.281551432215316</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -34809,11 +34809,11 @@
         <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>0.4201598676364207</v>
+        <v>0.4294721912747743</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -34957,11 +34957,11 @@
         <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>2.620677147737568</v>
+        <v>2.678761214377858</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -35105,11 +35105,11 @@
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>0.1865509812305708</v>
+        <v>0.1906856529259998</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -35253,11 +35253,11 @@
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>1.800525086111275</v>
+        <v>1.840431497009499</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -35401,11 +35401,11 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>0.07674920248825284</v>
+        <v>0.07845025360619209</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -35549,11 +35549,11 @@
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.005041918411637048</v>
+        <v>0.005153666295297291</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -35697,11 +35697,11 @@
         <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>8.841844254540836</v>
+        <v>9.037812793186349</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -35845,11 +35845,11 @@
         <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>3.888439521685861</v>
+        <v>3.974621972850944</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -35993,11 +35993,11 @@
         <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>0.5232390884965559</v>
+        <v>0.5348360355341856</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -36141,11 +36141,11 @@
         <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>2.11760573288756</v>
+        <v>2.164539844024862</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -36289,11 +36289,11 @@
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>0.1602209628586884</v>
+        <v>0.1637720622727806</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -36437,11 +36437,11 @@
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>1.279526850242113</v>
+        <v>1.307885979828779</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -36585,11 +36585,11 @@
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0.05546110252800752</v>
+        <v>0.05669032924827021</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -36733,11 +36733,11 @@
         <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>0.003921492097939926</v>
+        <v>0.00400840711856456</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
@@ -36881,11 +36881,11 @@
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>19.53851993516307</v>
+        <v>19.95291076874102</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -37029,11 +37029,11 @@
         <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>3.443089044707692</v>
+        <v>3.516113232008173</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
@@ -37177,11 +37177,11 @@
         <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>0.7529508121566909</v>
+        <v>0.7689200828961434</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -37325,11 +37325,11 @@
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>2.145909814646569</v>
+        <v>2.191422236254009</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -37473,11 +37473,11 @@
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0.2181342794042178</v>
+        <v>0.2227606710743239</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -37621,11 +37621,11 @@
         <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>1.658706347956946</v>
+        <v>1.693885712027092</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
@@ -37769,11 +37769,11 @@
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.07141959909427435</v>
+        <v>0.07293433139235478</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
@@ -37917,11 +37917,11 @@
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>0.001107280606112781</v>
+        <v>0.001130764827788446</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -38065,11 +38065,11 @@
         <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>39.37268379215826</v>
+        <v>40.20773574650157</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -38213,11 +38213,11 @@
         <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>3.999497549279364</v>
+        <v>4.084322557971868</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -38361,11 +38361,11 @@
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.9306693494377923</v>
+        <v>0.950407837756189</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -38509,11 +38509,11 @@
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>3.169590734997835</v>
+        <v>3.236814319544427</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
@@ -38657,11 +38657,11 @@
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0.2186879197072742</v>
+        <v>0.2233260534882181</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -38805,11 +38805,11 @@
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>1.598359554923799</v>
+        <v>1.632259028912622</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
@@ -38953,11 +38953,11 @@
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>0.1395173563702104</v>
+        <v>0.1424763683013442</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
@@ -39101,11 +39101,11 @@
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>0.001660920909169171</v>
+        <v>0.001696147241682669</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -39249,11 +39249,11 @@
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>49.58015005960893</v>
+        <v>50.63169131146936</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -39397,11 +39397,11 @@
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>3.821225371695206</v>
+        <v>3.902269420697928</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO263" t="inlineStr">
@@ -39545,11 +39545,11 @@
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.8791808012535479</v>
+        <v>0.8978272732640262</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
@@ -39693,11 +39693,11 @@
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>3.012910529232876</v>
+        <v>3.076811096412362</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
@@ -39841,11 +39841,11 @@
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>0.1865767821300036</v>
+        <v>0.1905338734823532</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -39989,11 +39989,11 @@
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>1.592269511590179</v>
+        <v>1.626039822359786</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO267" t="inlineStr">
@@ -40137,11 +40137,11 @@
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.0863678872767969</v>
+        <v>0.0881996565674988</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -40285,11 +40285,11 @@
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0.003321841818338342</v>
+        <v>0.003392294483365338</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
@@ -40433,11 +40433,11 @@
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>42.16856732259303</v>
+        <v>43.06291693666739</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
@@ -40581,11 +40581,11 @@
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>4.272995858989221</v>
+        <v>4.363621470435613</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO271" t="inlineStr">
@@ -40729,11 +40729,11 @@
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>0.5519793821472212</v>
+        <v>0.5636862666525404</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
@@ -40877,11 +40877,11 @@
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>2.826333747102873</v>
+        <v>2.886277222930009</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO273" t="inlineStr">
@@ -41025,11 +41025,11 @@
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>0.2292070854653456</v>
+        <v>0.2340683193522083</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -41173,11 +41173,11 @@
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>1.603895957954363</v>
+        <v>1.637912853051564</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
@@ -41321,11 +41321,11 @@
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>0.1085134993990525</v>
+        <v>0.1108149531232677</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
@@ -41469,11 +41469,11 @@
         <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>0.003875482121394732</v>
+        <v>0.003957676897259561</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
@@ -41617,11 +41617,11 @@
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>28.55123042861806</v>
+        <v>29.15677108452508</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -41765,11 +41765,11 @@
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>4.355488264144623</v>
+        <v>4.447863450105853</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -41913,11 +41913,11 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>0.4362685588084356</v>
+        <v>0.4455213421486477</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
@@ -42061,11 +42061,11 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>2.835191991951775</v>
+        <v>2.895323341552316</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -42209,11 +42209,11 @@
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>0.2386189706173043</v>
+        <v>0.2436798203884101</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
@@ -42357,11 +42357,11 @@
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>1.524171754314243</v>
+        <v>1.556497785450796</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO283" t="inlineStr">
@@ -42505,11 +42505,11 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>0.08526060667068412</v>
+        <v>0.08706889173971036</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
@@ -42653,11 +42653,11 @@
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>0.005536403030563904</v>
+        <v>0.005653824138942231</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
@@ -42801,11 +42801,11 @@
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>16.61917461714673</v>
+        <v>16.97164930027679</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
@@ -42949,11 +42949,11 @@
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>3.807938004421853</v>
+        <v>3.888700242764466</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
@@ -43097,11 +43097,11 @@
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>0.3631880388049921</v>
+        <v>0.3708908635146103</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -43245,11 +43245,11 @@
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>2.478093996480403</v>
+        <v>2.530651684590542</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
@@ -43393,11 +43393,11 @@
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>0.2607645827395599</v>
+        <v>0.2662951169441791</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
@@ -43541,11 +43541,11 @@
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>1.286660064303051</v>
+        <v>1.313948729890174</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO291" t="inlineStr">
@@ -43689,11 +43689,11 @@
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>0.08359968576151494</v>
+        <v>0.08537274449802769</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO292" t="inlineStr">
@@ -43837,11 +43837,11 @@
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>0.007197323939733075</v>
+        <v>0.007349971380624899</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
@@ -43985,11 +43985,11 @@
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>9.234166614677536</v>
+        <v>9.430013281341747</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -44133,11 +44133,11 @@
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>4.430783345360292</v>
+        <v>4.524755458395467</v>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
@@ -44281,11 +44281,11 @@
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>0.3975137375944883</v>
+        <v>0.4059445731760521</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -44429,11 +44429,11 @@
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>2.637542403760644</v>
+        <v>2.693481819792078</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">
@@ -44577,11 +44577,11 @@
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>0.2801419933465336</v>
+        <v>0.2860835014304769</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
@@ -44725,11 +44725,11 @@
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>1.377457074004299</v>
+        <v>1.406671445768827</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
@@ -44873,11 +44873,11 @@
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>0.08138512454928939</v>
+        <v>0.08311121484245079</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -45021,11 +45021,11 @@
         <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>0.004982762727507513</v>
+        <v>0.005088441725048008</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -45169,11 +45169,11 @@
         <v>0</v>
       </c>
       <c r="R302" t="n">
-        <v>5.818759585122663</v>
+        <v>5.942169170028285</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
@@ -45317,11 +45317,11 @@
         <v>0</v>
       </c>
       <c r="R303" t="n">
-        <v>4.235901958684443</v>
+        <v>4.325740848704701</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
@@ -45465,11 +45465,11 @@
         <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>0.3183431742574245</v>
+        <v>0.3250948879891782</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
@@ -45613,11 +45613,11 @@
         <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>2.715605686491595</v>
+        <v>2.773200740151164</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO305" t="inlineStr">
@@ -45761,11 +45761,11 @@
         <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>0.3144676921360298</v>
+        <v>0.3211372110919187</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -45909,11 +45909,11 @@
         <v>0</v>
       </c>
       <c r="R307" t="n">
-        <v>1.386315318853202</v>
+        <v>1.415717564391135</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO307" t="inlineStr">
@@ -46057,11 +46057,11 @@
         <v>0</v>
       </c>
       <c r="R308" t="n">
-        <v>0.106298938186827</v>
+        <v>0.1085534234676908</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO308" t="inlineStr">
@@ -46205,11 +46205,11 @@
         <v>0</v>
       </c>
       <c r="R309" t="n">
-        <v>0.003875482121394732</v>
+        <v>0.003957676897259561</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO309" t="inlineStr">
@@ -46353,11 +46353,11 @@
         <v>0</v>
       </c>
       <c r="R310" t="n">
-        <v>4.966707158718878</v>
+        <v>5.072045635045075</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -46501,11 +46501,11 @@
         <v>0</v>
       </c>
       <c r="R311" t="n">
-        <v>4.507185707182074</v>
+        <v>4.60277823151287</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO311" t="inlineStr">
@@ -46649,11 +46649,11 @@
         <v>0</v>
       </c>
       <c r="R312" t="n">
-        <v>0.3449179088041312</v>
+        <v>0.3522332438561009</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -46797,11 +46797,11 @@
         <v>0</v>
       </c>
       <c r="R313" t="n">
-        <v>2.908826152258275</v>
+        <v>2.970519202600248</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO313" t="inlineStr">
@@ -46945,11 +46945,11 @@
         <v>0</v>
       </c>
       <c r="R314" t="n">
-        <v>0.2591036618303907</v>
+        <v>0.2645989697024964</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -47093,11 +47093,11 @@
         <v>0</v>
       </c>
       <c r="R315" t="n">
-        <v>1.501472501888931</v>
+        <v>1.533317106481133</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO315" t="inlineStr">
@@ -47241,11 +47241,11 @@
         <v>0</v>
       </c>
       <c r="R316" t="n">
-        <v>0.1173717442479548</v>
+        <v>0.1198610717455753</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO316" t="inlineStr">
@@ -47389,11 +47389,11 @@
         <v>0</v>
       </c>
       <c r="R317" t="n">
-        <v>0.004429122424451123</v>
+        <v>0.004523059311153784</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
@@ -47537,11 +47537,11 @@
         <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>4.002819391097703</v>
+        <v>4.087714852455233</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -47685,11 +47685,11 @@
         <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>4.627879293248367</v>
+        <v>4.726031597741811</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO319" t="inlineStr">
@@ -47833,11 +47833,11 @@
         <v>0</v>
       </c>
       <c r="R320" t="n">
-        <v>0.3260941385002139</v>
+        <v>0.3330102417836974</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO320" t="inlineStr">
@@ -47981,11 +47981,11 @@
         <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>2.952010095896674</v>
+        <v>3.014619030883997</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO321" t="inlineStr">
@@ -48129,11 +48129,11 @@
         <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>0.3111458503176914</v>
+        <v>0.3177449166085534</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO322" t="inlineStr">
@@ -48277,11 +48277,11 @@
         <v>0</v>
       </c>
       <c r="R323" t="n">
-        <v>1.63656073583469</v>
+        <v>1.671270415471324</v>
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO323" t="inlineStr">
@@ -48425,11 +48425,11 @@
         <v>0</v>
       </c>
       <c r="R324" t="n">
-        <v>0.1600020475832968</v>
+        <v>0.1633955176154304</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO324" t="inlineStr">
@@ -48573,11 +48573,11 @@
         <v>0</v>
       </c>
       <c r="R325" t="n">
-        <v>0.001107280606112781</v>
+        <v>0.001130764827788446</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
@@ -48721,11 +48721,11 @@
         <v>0</v>
       </c>
       <c r="R326" t="n">
-        <v>4.658883150219525</v>
+        <v>4.757693012919887</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO326" t="inlineStr">
@@ -48869,11 +48869,11 @@
         <v>0</v>
       </c>
       <c r="R327" t="n">
-        <v>4.148980431104589</v>
+        <v>4.236975809723307</v>
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO327" t="inlineStr">
@@ -49017,11 +49017,11 @@
         <v>0</v>
       </c>
       <c r="R328" t="n">
-        <v>0.3637416791080485</v>
+        <v>0.3714562459285046</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO328" t="inlineStr">
@@ -49165,11 +49165,11 @@
         <v>0</v>
       </c>
       <c r="R329" t="n">
-        <v>2.671314462247083</v>
+        <v>2.727970147039626</v>
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO329" t="inlineStr">
@@ -49313,11 +49313,11 @@
         <v>0</v>
       </c>
       <c r="R330" t="n">
-        <v>0.232528927283684</v>
+        <v>0.2374606138355737</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO330" t="inlineStr">
@@ -49461,11 +49461,11 @@
         <v>0</v>
       </c>
       <c r="R331" t="n">
-        <v>1.659813628563058</v>
+        <v>1.695016476854881</v>
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO331" t="inlineStr">
@@ -49609,11 +49609,11 @@
         <v>0</v>
       </c>
       <c r="R332" t="n">
-        <v>0.1151571830357292</v>
+        <v>0.1175995420899984</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO332" t="inlineStr">
@@ -49757,11 +49757,11 @@
         <v>0</v>
       </c>
       <c r="R333" t="n">
-        <v>0.004429122424451123</v>
+        <v>0.004523059311153784</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO333" t="inlineStr">
@@ -49905,11 +49905,11 @@
         <v>0</v>
       </c>
       <c r="R334" t="n">
-        <v>6.13987096089537</v>
+        <v>6.270090970086934</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO334" t="inlineStr">
@@ -50053,11 +50053,11 @@
         <v>0</v>
       </c>
       <c r="R335" t="n">
-        <v>4.081989954434766</v>
+        <v>4.168564537642107</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO335" t="inlineStr">
@@ -50201,11 +50201,11 @@
         <v>0</v>
       </c>
       <c r="R336" t="n">
-        <v>0.4185520691106312</v>
+        <v>0.4274291049040326</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO336" t="inlineStr">
@@ -50349,11 +50349,11 @@
         <v>0</v>
       </c>
       <c r="R337" t="n">
-        <v>2.248886911015058</v>
+        <v>2.296583365238334</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO337" t="inlineStr">
@@ -50497,11 +50497,11 @@
         <v>0</v>
       </c>
       <c r="R338" t="n">
-        <v>0.2231170421317253</v>
+        <v>0.2278491127993719</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO338" t="inlineStr">
@@ -50645,11 +50645,11 @@
         <v>0</v>
       </c>
       <c r="R339" t="n">
-        <v>1.311573877940589</v>
+        <v>1.339390938515415</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO339" t="inlineStr">
@@ -50793,11 +50793,11 @@
         <v>0</v>
       </c>
       <c r="R340" t="n">
-        <v>0.0979943336409811</v>
+        <v>0.1000726872592775</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO340" t="inlineStr">
@@ -50941,11 +50941,11 @@
         <v>0</v>
       </c>
       <c r="R341" t="n">
-        <v>0.003875482121394732</v>
+        <v>0.003957676897259561</v>
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO341" t="inlineStr">
@@ -51089,11 +51089,11 @@
         <v>0</v>
       </c>
       <c r="R342" t="n">
-        <v>7.591618526884087</v>
+        <v>7.63786534198867</v>
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO342" t="inlineStr">
@@ -51237,11 +51237,11 @@
         <v>0</v>
       </c>
       <c r="R343" t="n">
-        <v>3.075952156227408</v>
+        <v>3.09469031991883</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO343" t="inlineStr">
@@ -51385,11 +51385,11 @@
         <v>0</v>
       </c>
       <c r="R344" t="n">
-        <v>0.7171200079476604</v>
+        <v>0.7214885778774991</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO344" t="inlineStr">
@@ -51533,11 +51533,11 @@
         <v>0</v>
       </c>
       <c r="R345" t="n">
-        <v>0.2162308420910884</v>
+        <v>0.217548082642452</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
@@ -51681,11 +51681,11 @@
         <v>0</v>
       </c>
       <c r="R346" t="n">
-        <v>2.157381642230328</v>
+        <v>2.17052403466811</v>
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO346" t="inlineStr">
@@ -51829,11 +51829,11 @@
         <v>0</v>
       </c>
       <c r="R347" t="n">
-        <v>0.2348431171065239</v>
+        <v>0.236273740388891</v>
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO347" t="inlineStr">
@@ -51977,11 +51977,11 @@
         <v>0</v>
       </c>
       <c r="R348" t="n">
-        <v>1.540439467453982</v>
+        <v>1.54982355583762</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO348" t="inlineStr">
@@ -52125,11 +52125,11 @@
         <v>0</v>
       </c>
       <c r="R349" t="n">
-        <v>0.07061716108797572</v>
+        <v>0.07104734850854763</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO349" t="inlineStr">
@@ -52273,11 +52273,11 @@
         <v>0</v>
       </c>
       <c r="R350" t="n">
-        <v>0.002189679413580642</v>
+        <v>0.002203018558404578</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO350" t="inlineStr">
@@ -52421,11 +52421,11 @@
         <v>0</v>
       </c>
       <c r="R351" t="n">
-        <v>10.33200231298026</v>
+        <v>10.394943067832</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO351" t="inlineStr">
@@ -52569,11 +52569,11 @@
         <v>0</v>
       </c>
       <c r="R352" t="n">
-        <v>3.246747150486697</v>
+        <v>3.266525767474387</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO352" t="inlineStr">
@@ -52717,11 +52717,11 @@
         <v>0</v>
       </c>
       <c r="R353" t="n">
-        <v>1.098671645764087</v>
+        <v>1.105364561679497</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO353" t="inlineStr">
@@ -52865,11 +52865,11 @@
         <v>0</v>
       </c>
       <c r="R354" t="n">
-        <v>0.1833856508873788</v>
+        <v>0.1845028042663834</v>
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO354" t="inlineStr">
@@ -53013,11 +53013,11 @@
         <v>0</v>
       </c>
       <c r="R355" t="n">
-        <v>2.307374682060602</v>
+        <v>2.321430805918824</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO355" t="inlineStr">
@@ -53161,11 +53161,11 @@
         <v>0</v>
       </c>
       <c r="R356" t="n">
-        <v>0.2260843994522014</v>
+        <v>0.2274616661552726</v>
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO356" t="inlineStr">
@@ -53309,11 +53309,11 @@
         <v>0</v>
       </c>
       <c r="R357" t="n">
-        <v>1.371834152608272</v>
+        <v>1.380191126840468</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO357" t="inlineStr">
@@ -53457,11 +53457,11 @@
         <v>0</v>
       </c>
       <c r="R358" t="n">
-        <v>0.08375523756945957</v>
+        <v>0.08426545985897509</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO358" t="inlineStr">
@@ -53605,11 +53605,11 @@
         <v>0</v>
       </c>
       <c r="R359" t="n">
-        <v>0.001642259560185482</v>
+        <v>0.001652263918803433</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO359" t="inlineStr">
@@ -53753,11 +53753,11 @@
         <v>0</v>
       </c>
       <c r="R360" t="n">
-        <v>15.26808713104442</v>
+        <v>15.36109765311552</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO360" t="inlineStr">
@@ -53901,11 +53901,11 @@
         <v>0</v>
       </c>
       <c r="R361" t="n">
-        <v>4.485558278719946</v>
+        <v>4.512883516891777</v>
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO361" t="inlineStr">
@@ -54049,11 +54049,11 @@
         <v>0</v>
       </c>
       <c r="R362" t="n">
-        <v>0.8572594904168215</v>
+        <v>0.862481765615392</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO362" t="inlineStr">
@@ -54197,11 +54197,11 @@
         <v>0</v>
       </c>
       <c r="R363" t="n">
-        <v>0.1888598494213304</v>
+        <v>0.1900103506623948</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO363" t="inlineStr">
@@ -54345,11 +54345,11 @@
         <v>0</v>
       </c>
       <c r="R364" t="n">
-        <v>3.002050476019061</v>
+        <v>3.020338443572676</v>
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO364" t="inlineStr">
@@ -54493,11 +54493,11 @@
         <v>0</v>
       </c>
       <c r="R365" t="n">
-        <v>0.3076499576080803</v>
+        <v>0.3095241074558431</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO365" t="inlineStr">
@@ -54641,11 +54641,11 @@
         <v>0</v>
       </c>
       <c r="R366" t="n">
-        <v>1.825097791219465</v>
+        <v>1.836215968430215</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO366" t="inlineStr">
@@ -54789,11 +54789,11 @@
         <v>0</v>
       </c>
       <c r="R367" t="n">
-        <v>0.08977685595680633</v>
+        <v>0.09032376089458767</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO367" t="inlineStr">
@@ -54937,11 +54937,11 @@
         <v>0</v>
       </c>
       <c r="R368" t="n">
-        <v>0.002737099266975803</v>
+        <v>0.002753773198005722</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO368" t="inlineStr">
@@ -55085,11 +55085,11 @@
         <v>0</v>
       </c>
       <c r="R369" t="n">
-        <v>9.06965213105102</v>
+        <v>9.124902868911761</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO369" t="inlineStr">
@@ -55233,11 +55233,11 @@
         <v>0</v>
       </c>
       <c r="R370" t="n">
-        <v>4.22717610791743</v>
+        <v>4.252927327000037</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO370" t="inlineStr">
@@ -55381,11 +55381,11 @@
         <v>0</v>
       </c>
       <c r="R371" t="n">
-        <v>0.562747609290225</v>
+        <v>0.5661757695099765</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO371" t="inlineStr">
@@ -55529,11 +55529,11 @@
         <v>0</v>
       </c>
       <c r="R372" t="n">
-        <v>0.1653207957253385</v>
+        <v>0.1663279011595456</v>
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO372" t="inlineStr">
@@ -55677,11 +55677,11 @@
         <v>0</v>
       </c>
       <c r="R373" t="n">
-        <v>2.534553921219594</v>
+        <v>2.549993981353298</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO373" t="inlineStr">
@@ -55825,11 +55825,11 @@
         <v>0</v>
       </c>
       <c r="R374" t="n">
-        <v>0.2633089494830723</v>
+        <v>0.2649129816481504</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO374" t="inlineStr">
@@ -55973,11 +55973,11 @@
         <v>0</v>
       </c>
       <c r="R375" t="n">
-        <v>1.452852290910756</v>
+        <v>1.461702813501437</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO375" t="inlineStr">
@@ -56121,11 +56121,11 @@
         <v>0</v>
       </c>
       <c r="R376" t="n">
-        <v>0.07828103903550797</v>
+        <v>0.07875791346296364</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO376" t="inlineStr">
@@ -56269,11 +56269,11 @@
         <v>0</v>
       </c>
       <c r="R377" t="n">
-        <v>0.004926778680556446</v>
+        <v>0.004956791756410299</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO377" t="inlineStr">
@@ -56417,11 +56417,11 @@
         <v>0</v>
       </c>
       <c r="R378" t="n">
-        <v>7.185432995664877</v>
+        <v>7.229205399404621</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO378" t="inlineStr">
@@ -56565,11 +56565,11 @@
         <v>0</v>
       </c>
       <c r="R379" t="n">
-        <v>4.211848352022366</v>
+        <v>4.237506197091204</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO379" t="inlineStr">
@@ -56713,11 +56713,11 @@
         <v>0</v>
       </c>
       <c r="R380" t="n">
-        <v>0.5266178989661445</v>
+        <v>0.5298259632963008</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO380" t="inlineStr">
@@ -56861,11 +56861,11 @@
         <v>0</v>
       </c>
       <c r="R381" t="n">
-        <v>0.177364032500032</v>
+        <v>0.1784445032307708</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO381" t="inlineStr">
@@ -57009,11 +57009,11 @@
         <v>0</v>
       </c>
       <c r="R382" t="n">
-        <v>3.03270598780919</v>
+        <v>3.05118070339034</v>
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO382" t="inlineStr">
@@ -57157,11 +57157,11 @@
         <v>0</v>
       </c>
       <c r="R383" t="n">
-        <v>0.2835634840586932</v>
+        <v>0.2852909033133927</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO383" t="inlineStr">
@@ -57305,11 +57305,11 @@
         <v>0</v>
       </c>
       <c r="R384" t="n">
-        <v>1.275488258410724</v>
+        <v>1.283258310270666</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO384" t="inlineStr">
@@ -57453,11 +57453,11 @@
         <v>0</v>
       </c>
       <c r="R385" t="n">
-        <v>0.102367512584895</v>
+        <v>0.102991117605414</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO385" t="inlineStr">
@@ -57601,11 +57601,11 @@
         <v>0</v>
       </c>
       <c r="R386" t="n">
-        <v>0.006569038240741927</v>
+        <v>0.006609055675213733</v>
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO386" t="inlineStr">
@@ -57749,11 +57749,11 @@
         <v>0</v>
       </c>
       <c r="R387" t="n">
-        <v>4.226081268210639</v>
+        <v>4.251825817720834</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO387" t="inlineStr">
@@ -57897,11 +57897,11 @@
         <v>0</v>
       </c>
       <c r="R388" t="n">
-        <v>3.879017081158108</v>
+        <v>3.902647376213709</v>
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO388" t="inlineStr">
@@ -58045,11 +58045,11 @@
         <v>0</v>
       </c>
       <c r="R389" t="n">
-        <v>0.4986994864429913</v>
+        <v>0.5017374766766425</v>
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO389" t="inlineStr">
@@ -58193,11 +58193,11 @@
         <v>0</v>
       </c>
       <c r="R390" t="n">
-        <v>0.1428765817361369</v>
+        <v>0.1437469609358987</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO390" t="inlineStr">
@@ -58341,11 +58341,11 @@
         <v>0</v>
       </c>
       <c r="R391" t="n">
-        <v>2.824139023665634</v>
+        <v>2.841343185702304</v>
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO391" t="inlineStr">
@@ -58489,11 +58489,11 @@
         <v>0</v>
       </c>
       <c r="R392" t="n">
-        <v>0.2791841252315319</v>
+        <v>0.2808848661965836</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO392" t="inlineStr">
@@ -58637,11 +58637,11 @@
         <v>0</v>
       </c>
       <c r="R393" t="n">
-        <v>1.100313905324273</v>
+        <v>1.1070168255983</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO393" t="inlineStr">
@@ -58785,11 +58785,11 @@
         <v>0</v>
       </c>
       <c r="R394" t="n">
-        <v>0.1149581692129837</v>
+        <v>0.1156584743162403</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO394" t="inlineStr">
@@ -58933,11 +58933,11 @@
         <v>0</v>
       </c>
       <c r="R395" t="n">
-        <v>0.007663877947532248</v>
+        <v>0.007710564954416021</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO395" t="inlineStr">
@@ -59081,11 +59081,11 @@
         <v>0</v>
       </c>
       <c r="R396" t="n">
-        <v>3.025589529715053</v>
+        <v>3.044020893075525</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO396" t="inlineStr">
@@ -59229,11 +59229,11 @@
         <v>0</v>
       </c>
       <c r="R397" t="n">
-        <v>4.204731893928228</v>
+        <v>4.23034638677639</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO397" t="inlineStr">
@@ -59377,11 +59377,11 @@
         <v>0</v>
       </c>
       <c r="R398" t="n">
-        <v>0.5917608615201686</v>
+        <v>0.595365765408837</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO398" t="inlineStr">
@@ -59525,11 +59525,11 @@
         <v>0</v>
       </c>
       <c r="R399" t="n">
-        <v>0.1992608266358385</v>
+        <v>0.2004746888148165</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO399" t="inlineStr">
@@ -59673,11 +59673,11 @@
         <v>0</v>
       </c>
       <c r="R400" t="n">
-        <v>2.746952824336916</v>
+        <v>2.763686781518543</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO400" t="inlineStr">
@@ -59821,11 +59821,11 @@
         <v>0</v>
       </c>
       <c r="R401" t="n">
-        <v>0.2846583237654836</v>
+        <v>0.2863924125925951</v>
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO401" t="inlineStr">
@@ -59969,11 +59969,11 @@
         <v>0</v>
       </c>
       <c r="R402" t="n">
-        <v>1.1424652340357</v>
+        <v>1.149424932847588</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO402" t="inlineStr">
@@ -60117,11 +60117,11 @@
         <v>0</v>
       </c>
       <c r="R403" t="n">
-        <v>0.09196653537038699</v>
+        <v>0.09252677945299226</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO403" t="inlineStr">
@@ -60265,11 +60265,11 @@
         <v>0</v>
       </c>
       <c r="R404" t="n">
-        <v>0.01697001545524998</v>
+        <v>0.01707339382763548</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO404" t="inlineStr">
@@ -60413,11 +60413,11 @@
         <v>0</v>
       </c>
       <c r="R405" t="n">
-        <v>2.7600909008184</v>
+        <v>2.77690489286897</v>
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO405" t="inlineStr">
@@ -60561,11 +60561,11 @@
         <v>0</v>
       </c>
       <c r="R406" t="n">
-        <v>4.469683102971486</v>
+        <v>4.496911632343344</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO406" t="inlineStr">
@@ -60709,11 +60709,11 @@
         <v>0</v>
       </c>
       <c r="R407" t="n">
-        <v>0.4631171959723059</v>
+        <v>0.4659384251025682</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO407" t="inlineStr">
@@ -60857,11 +60857,11 @@
         <v>0</v>
       </c>
       <c r="R408" t="n">
-        <v>0.1631311163117579</v>
+        <v>0.164124882601141</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO408" t="inlineStr">
@@ -61005,11 +61005,11 @@
         <v>0</v>
       </c>
       <c r="R409" t="n">
-        <v>3.132883820980504</v>
+        <v>3.151968802437349</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO409" t="inlineStr">
@@ -61153,11 +61153,11 @@
         <v>0</v>
       </c>
       <c r="R410" t="n">
-        <v>0.2939644612732012</v>
+        <v>0.2957552414658145</v>
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO410" t="inlineStr">
@@ -61301,11 +61301,11 @@
         <v>0</v>
       </c>
       <c r="R411" t="n">
-        <v>1.307238609907643</v>
+        <v>1.315202079367533</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO411" t="inlineStr">
@@ -61449,11 +61449,11 @@
         <v>0</v>
       </c>
       <c r="R412" t="n">
-        <v>0.09360879493057246</v>
+        <v>0.09417904337179568</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO412" t="inlineStr">
@@ -61597,11 +61597,11 @@
         <v>0</v>
       </c>
       <c r="R413" t="n">
-        <v>0.01423291618827418</v>
+        <v>0.01431962062962975</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO413" t="inlineStr">
@@ -61745,11 +61745,11 @@
         <v>0</v>
       </c>
       <c r="R414" t="n">
-        <v>2.416311232886239</v>
+        <v>2.431030979199451</v>
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO414" t="inlineStr">
@@ -61893,11 +61893,11 @@
         <v>0</v>
       </c>
       <c r="R415" t="n">
-        <v>4.376074308040914</v>
+        <v>4.402732588971548</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO415" t="inlineStr">
@@ -62041,11 +62041,11 @@
         <v>0</v>
       </c>
       <c r="R416" t="n">
-        <v>0.4357462033025479</v>
+        <v>0.4384006931225109</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO416" t="inlineStr">
@@ -62189,11 +62189,11 @@
         <v>0</v>
       </c>
       <c r="R417" t="n">
-        <v>0.1527301390972498</v>
+        <v>0.1536605444487193</v>
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO417" t="inlineStr">
@@ -62337,11 +62337,11 @@
         <v>0</v>
       </c>
       <c r="R418" t="n">
-        <v>2.668671785301408</v>
+        <v>2.684928868055579</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO418" t="inlineStr">
@@ -62485,11 +62485,11 @@
         <v>0</v>
       </c>
       <c r="R419" t="n">
-        <v>0.2852057436188787</v>
+        <v>0.2869431672321962</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO419" t="inlineStr">
@@ -62633,11 +62633,11 @@
         <v>0</v>
       </c>
       <c r="R420" t="n">
-        <v>1.254138884128313</v>
+        <v>1.261778879326222</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO420" t="inlineStr">
@@ -62781,11 +62781,11 @@
         <v>0</v>
       </c>
       <c r="R421" t="n">
-        <v>0.09634589419754827</v>
+        <v>0.09693281656980141</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO421" t="inlineStr">
@@ -62929,11 +62929,11 @@
         <v>0</v>
       </c>
       <c r="R422" t="n">
-        <v>0.01259065662808869</v>
+        <v>0.01266735671082632</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO422" t="inlineStr">
@@ -63077,11 +63077,11 @@
         <v>0</v>
       </c>
       <c r="R423" t="n">
-        <v>2.566851692569908</v>
+        <v>2.582488505089766</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO423" t="inlineStr">
@@ -63225,11 +63225,11 @@
         <v>0</v>
       </c>
       <c r="R424" t="n">
-        <v>4.286844871937503</v>
+        <v>4.312959582716561</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO424" t="inlineStr">
@@ -63373,11 +63373,11 @@
         <v>0</v>
       </c>
       <c r="R425" t="n">
-        <v>0.3415899885185802</v>
+        <v>0.3436708951111141</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO425" t="inlineStr">
@@ -63521,11 +63521,11 @@
         <v>0</v>
       </c>
       <c r="R426" t="n">
-        <v>0.1215272074537257</v>
+        <v>0.122267529991454</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO426" t="inlineStr">
@@ -63669,11 +63669,11 @@
         <v>0</v>
       </c>
       <c r="R427" t="n">
-        <v>2.316133399714924</v>
+        <v>2.330242880152442</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO427" t="inlineStr">
@@ -63817,11 +63817,11 @@
         <v>0</v>
       </c>
       <c r="R428" t="n">
-        <v>0.2682357281636287</v>
+        <v>0.2698697734045608</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO428" t="inlineStr">
@@ -63965,11 +63965,11 @@
         <v>0</v>
       </c>
       <c r="R429" t="n">
-        <v>1.324756045216289</v>
+        <v>1.332826227834769</v>
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO429" t="inlineStr">
@@ -64113,11 +64113,11 @@
         <v>0</v>
       </c>
       <c r="R430" t="n">
-        <v>0.08156555815587893</v>
+        <v>0.08206244130057051</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO430" t="inlineStr">
@@ -64261,11 +64261,11 @@
         <v>0</v>
       </c>
       <c r="R431" t="n">
-        <v>0.01040097721450805</v>
+        <v>0.01046433815242174</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO431" t="inlineStr">
@@ -64409,11 +64409,11 @@
         <v>0</v>
       </c>
       <c r="R432" t="n">
-        <v>4.928420940116632</v>
+        <v>4.958444020329103</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO432" t="inlineStr">
@@ -64557,11 +64557,11 @@
         <v>0</v>
       </c>
       <c r="R433" t="n">
-        <v>4.307099406513124</v>
+        <v>4.333337504381804</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO433" t="inlineStr">
@@ -64705,11 +64705,11 @@
         <v>0</v>
       </c>
       <c r="R434" t="n">
-        <v>0.3963319738580963</v>
+        <v>0.3987463590712285</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO434" t="inlineStr">
@@ -64853,11 +64853,11 @@
         <v>0</v>
       </c>
       <c r="R435" t="n">
-        <v>0.1302859251080482</v>
+        <v>0.1310796042250723</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO435" t="inlineStr">
@@ -65001,11 +65001,11 @@
         <v>0</v>
       </c>
       <c r="R436" t="n">
-        <v>2.525795203565271</v>
+        <v>2.54118190711968</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO436" t="inlineStr">
@@ -65149,11 +65149,11 @@
         <v>0</v>
       </c>
       <c r="R437" t="n">
-        <v>0.2408647354938707</v>
+        <v>0.2423320414245035</v>
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO437" t="inlineStr">
@@ -65297,11 +65297,11 @@
         <v>0</v>
       </c>
       <c r="R438" t="n">
-        <v>1.674009911682401</v>
+        <v>1.6842076879003</v>
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO438" t="inlineStr">
@@ -65445,11 +65445,11 @@
         <v>0</v>
       </c>
       <c r="R439" t="n">
-        <v>0.09963041331791923</v>
+        <v>0.1002373444074083</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO439" t="inlineStr">
@@ -65593,11 +65593,11 @@
         <v>0</v>
       </c>
       <c r="R440" t="n">
-        <v>0.01040097721450805</v>
+        <v>0.01046433815242174</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO440" t="inlineStr">
@@ -65741,11 +65741,11 @@
         <v>0</v>
       </c>
       <c r="R441" t="n">
-        <v>5.553574412693904</v>
+        <v>5.587405818753609</v>
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO441" t="inlineStr">
@@ -65889,11 +65889,11 @@
         <v>0</v>
       </c>
       <c r="R442" t="n">
-        <v>4.016419464360293</v>
+        <v>4.040886790753596</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO442" t="inlineStr">
@@ -66037,11 +66037,11 @@
         <v>0</v>
       </c>
       <c r="R443" t="n">
-        <v>0.4007113326852575</v>
+        <v>0.4031523961880377</v>
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO443" t="inlineStr">
@@ -66185,11 +66185,11 @@
         <v>0</v>
       </c>
       <c r="R444" t="n">
-        <v>0.2019979259028143</v>
+        <v>0.2032284620128223</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO444" t="inlineStr">
@@ -66333,11 +66333,11 @@
         <v>0</v>
       </c>
       <c r="R445" t="n">
-        <v>2.24989559745411</v>
+        <v>2.263601568760703</v>
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO445" t="inlineStr">
@@ -66481,11 +66481,11 @@
         <v>0</v>
       </c>
       <c r="R446" t="n">
-        <v>0.2255369795988062</v>
+        <v>0.2269109115156715</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO446" t="inlineStr">
@@ -66629,11 +66629,11 @@
         <v>0</v>
       </c>
       <c r="R447" t="n">
-        <v>1.309428289321224</v>
+        <v>1.317405097925938</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO447" t="inlineStr">
@@ -66777,11 +66777,11 @@
         <v>0</v>
       </c>
       <c r="R448" t="n">
-        <v>0.08101813830248376</v>
+        <v>0.08151168666096938</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO448" t="inlineStr">
@@ -66925,11 +66925,11 @@
         <v>0</v>
       </c>
       <c r="R449" t="n">
-        <v>0.00930613750771773</v>
+        <v>0.009362828873219455</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO449" t="inlineStr">

--- a/countries/br/2000-2004.xlsx
+++ b/countries/br/2000-2004.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15132,6 +15617,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15770,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15923,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16076,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +16229,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16382,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16020,6 +16535,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16688,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16316,6 +16841,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16994,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16612,6 +17147,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16760,6 +17300,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16908,6 +17453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17204,6 +17759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17500,6 +18065,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17648,6 +18218,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17796,6 +18371,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18524,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18092,6 +18677,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18830,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18388,6 +18983,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +19136,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18684,6 +19289,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19442,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18980,6 +19595,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19128,6 +19748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19276,6 +19901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +20054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19572,6 +20207,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +20360,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +20513,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20016,6 +20666,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20164,6 +20819,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20972,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20460,6 +21125,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +21278,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20756,6 +21431,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20904,6 +21584,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21737,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21890,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21348,6 +22043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21496,6 +22196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21644,6 +22349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21792,6 +22502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21940,6 +22655,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22808,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22236,6 +22961,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22384,6 +23114,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22532,6 +23267,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +23420,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22828,6 +23573,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23726,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23124,6 +23879,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23272,6 +24032,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23420,6 +24185,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +24338,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +24491,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23864,6 +24644,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24797,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24308,6 +25103,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25256,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24604,6 +25409,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24752,6 +25562,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24900,6 +25715,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25868,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25196,6 +26021,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +26174,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25492,6 +26327,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25640,6 +26480,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25788,6 +26633,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26786,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26084,6 +26939,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26232,6 +27092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26380,6 +27245,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26528,6 +27398,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27551,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +27704,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26972,6 +27857,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +28010,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27268,6 +28163,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27416,6 +28316,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27564,6 +28469,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +28622,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27860,6 +28775,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28008,6 +28928,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28156,6 +29081,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +29234,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28452,6 +29387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28600,6 +29540,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28748,6 +29693,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28896,6 +29846,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29044,6 +29999,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +30152,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29340,6 +30305,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +30458,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29636,6 +30611,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29784,6 +30764,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29932,6 +30917,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +31070,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30228,6 +31223,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30376,6 +31376,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30524,6 +31529,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +31682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31835,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30968,6 +31988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31116,6 +32141,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31264,6 +32294,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31412,6 +32447,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31560,6 +32600,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31708,6 +32753,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31856,6 +32906,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32004,6 +33059,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32152,6 +33212,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32300,6 +33365,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32448,6 +33518,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32596,6 +33671,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32744,6 +33824,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32892,6 +33977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33040,6 +34130,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33188,6 +34283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33336,6 +34436,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33484,6 +34589,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33632,6 +34742,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33780,6 +34895,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33928,6 +35048,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34076,6 +35201,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34224,6 +35354,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34372,6 +35507,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34520,6 +35660,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34668,6 +35813,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34816,6 +35966,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34964,6 +36119,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35112,6 +36272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35260,6 +36425,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35408,6 +36578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35556,6 +36731,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35704,6 +36884,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35852,6 +37037,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36000,6 +37190,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36148,6 +37343,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36296,6 +37496,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36444,6 +37649,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36592,6 +37802,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36740,6 +37955,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36888,6 +38108,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37036,6 +38261,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37184,6 +38414,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37332,6 +38567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37480,6 +38720,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37628,6 +38873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37776,6 +39026,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37924,6 +39179,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38072,6 +39332,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38220,6 +39485,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38368,6 +39638,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38516,6 +39791,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38664,6 +39944,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38812,6 +40097,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38960,6 +40250,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39108,6 +40403,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39256,6 +40556,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39404,6 +40709,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39552,6 +40862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39700,6 +41015,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39848,6 +41168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39996,6 +41321,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40144,6 +41474,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40292,6 +41627,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40440,6 +41780,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40588,6 +41933,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40736,6 +42086,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40884,6 +42239,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41032,6 +42392,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41180,6 +42545,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41328,6 +42698,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41476,6 +42851,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41624,6 +43004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41772,6 +43157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41920,6 +43310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42068,6 +43463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42216,6 +43616,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42364,6 +43769,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42512,6 +43922,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42660,6 +44075,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42808,6 +44228,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42956,6 +44381,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43104,6 +44534,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43252,6 +44687,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43400,6 +44840,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43548,6 +44993,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43696,6 +45146,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43844,6 +45299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43992,6 +45452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44140,6 +45605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44288,6 +45758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44436,6 +45911,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44584,6 +46064,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44732,6 +46217,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44880,6 +46370,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45028,6 +46523,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45176,6 +46676,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45324,6 +46829,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45472,6 +46982,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45620,6 +47135,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45768,6 +47288,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45916,6 +47441,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46064,6 +47594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46212,6 +47747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46360,6 +47900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46508,6 +48053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46656,6 +48206,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46804,6 +48359,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46952,6 +48512,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47100,6 +48665,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47248,6 +48818,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47396,6 +48971,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47544,6 +49124,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47692,6 +49277,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47840,6 +49430,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47988,6 +49583,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48136,6 +49736,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48284,6 +49889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48432,6 +50042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48580,6 +50195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48728,6 +50348,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48876,6 +50501,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49024,6 +50654,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49172,6 +50807,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49320,6 +50960,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49468,6 +51113,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49616,6 +51266,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49764,6 +51419,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49912,6 +51572,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50060,6 +51725,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50208,6 +51878,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50356,6 +52031,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50504,6 +52184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50652,6 +52337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50800,6 +52490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50948,6 +52643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51096,6 +52796,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51244,6 +52949,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51392,6 +53102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51540,6 +53255,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51688,6 +53408,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51836,6 +53561,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51984,6 +53714,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52132,6 +53867,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52280,6 +54020,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52428,6 +54173,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52576,6 +54326,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52724,6 +54479,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52872,6 +54632,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53020,6 +54785,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53168,6 +54938,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53316,6 +55091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53464,6 +55244,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53612,6 +55397,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53760,6 +55550,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53908,6 +55703,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54056,6 +55856,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54204,6 +56009,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54352,6 +56162,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54500,6 +56315,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54648,6 +56468,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54796,6 +56621,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54944,6 +56774,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55092,6 +56927,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55240,6 +57080,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55388,6 +57233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55536,6 +57386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55684,6 +57539,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55832,6 +57692,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55980,6 +57845,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56128,6 +57998,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56276,6 +58151,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56424,6 +58304,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56572,6 +58457,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56720,6 +58610,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56868,6 +58763,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57016,6 +58916,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57164,6 +59069,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57312,6 +59222,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57460,6 +59375,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57608,6 +59528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57756,6 +59681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57904,6 +59834,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58052,6 +59987,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58200,6 +60140,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58348,6 +60293,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58496,6 +60446,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58644,6 +60599,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58792,6 +60752,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58940,6 +60905,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59088,6 +61058,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59236,6 +61211,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59384,6 +61364,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59532,6 +61517,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59680,6 +61670,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59828,6 +61823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59976,6 +61976,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO402" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60124,6 +62129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60272,6 +62282,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60420,6 +62435,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60568,6 +62588,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60716,6 +62741,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60864,6 +62894,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61012,6 +63047,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61160,6 +63200,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61308,6 +63353,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61456,6 +63506,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61604,6 +63659,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61752,6 +63812,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61900,6 +63965,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62048,6 +64118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62196,6 +64271,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO417" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62344,6 +64424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62492,6 +64577,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62640,6 +64730,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62788,6 +64883,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62936,6 +65036,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63084,6 +65189,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63232,6 +65342,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63380,6 +65495,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63528,6 +65648,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63676,6 +65801,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63824,6 +65954,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63972,6 +66107,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64120,6 +66260,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64268,6 +66413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64416,6 +66566,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64564,6 +66719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64712,6 +66872,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64860,6 +67025,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65008,6 +67178,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65156,6 +67331,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65304,6 +67484,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65452,6 +67637,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65600,6 +67790,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65748,6 +67943,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65896,6 +68096,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66044,6 +68249,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66192,6 +68402,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66340,6 +68555,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66488,6 +68708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66636,6 +68861,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66784,6 +69014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66930,6 +69165,11 @@
       <c r="S449" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO449" t="inlineStr">
